--- a/data/processed/harmonization/Nitrogen__Carbon_to_nitrogen_ratio/dois_filtering.xlsx
+++ b/data/processed/harmonization/Nitrogen__Carbon_to_nitrogen_ratio/dois_filtering.xlsx
@@ -1065,7 +1065,7 @@
         <v>46</v>
       </c>
       <c r="D20">
-        <v>778</v>
+        <v>789</v>
       </c>
       <c r="E20" t="s">
         <v>79</v>
